--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -5185,7 +5185,7 @@
         <v>136356702</v>
       </c>
       <c r="B42" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136356995</v>
       </c>
       <c r="B56" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136455202</v>
       </c>
       <c r="B57" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>136665861</v>
       </c>
       <c r="B58" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>136356269</v>
       </c>
       <c r="B98" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>136356315</v>
       </c>
       <c r="B99" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>136356351</v>
       </c>
       <c r="B100" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>136356430</v>
       </c>
       <c r="B101" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>136357307</v>
       </c>
       <c r="B102" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>136357556</v>
       </c>
       <c r="B103" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>136358081</v>
       </c>
       <c r="B104" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>136455012</v>
       </c>
       <c r="B105" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>136455283</v>
       </c>
       <c r="B106" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>136455805</v>
       </c>
       <c r="B107" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>136665864</v>
       </c>
       <c r="B108" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>136665865</v>
       </c>
       <c r="B109" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>136358182</v>
       </c>
       <c r="B129" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>136359040</v>
       </c>
       <c r="B130" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>136356211</v>
       </c>
       <c r="B148" t="n">
-        <v>93429</v>
+        <v>93432</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>136357506</v>
       </c>
       <c r="B149" t="n">
-        <v>93429</v>
+        <v>93432</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>136358191</v>
       </c>
       <c r="B150" t="n">
-        <v>93429</v>
+        <v>93432</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>136665866</v>
       </c>
       <c r="B151" t="n">
-        <v>92768</v>
+        <v>92771</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>136358859</v>
       </c>
       <c r="B162" t="n">
-        <v>93384</v>
+        <v>93387</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>136583701</v>
       </c>
       <c r="B163" t="n">
-        <v>93384</v>
+        <v>93387</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>136357484</v>
       </c>
       <c r="B195" t="n">
-        <v>106472</v>
+        <v>106475</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>136358853</v>
       </c>
       <c r="B196" t="n">
-        <v>93431</v>
+        <v>93434</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ205"/>
+  <dimension ref="A1:AZ206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5185,7 +5185,7 @@
         <v>136356702</v>
       </c>
       <c r="B42" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>136356995</v>
       </c>
       <c r="B56" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>136455202</v>
       </c>
       <c r="B57" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>136665861</v>
       </c>
       <c r="B58" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>136356269</v>
       </c>
       <c r="B98" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>136356315</v>
       </c>
       <c r="B99" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>136356351</v>
       </c>
       <c r="B100" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>136356430</v>
       </c>
       <c r="B101" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>136357307</v>
       </c>
       <c r="B102" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>136357556</v>
       </c>
       <c r="B103" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>136358081</v>
       </c>
       <c r="B104" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>136455012</v>
       </c>
       <c r="B105" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>136455283</v>
       </c>
       <c r="B106" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>136455805</v>
       </c>
       <c r="B107" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>136665864</v>
       </c>
       <c r="B108" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>136665865</v>
       </c>
       <c r="B109" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12565,45 +12565,54 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120533224</v>
+        <v>136713127</v>
       </c>
       <c r="B110" t="n">
-        <v>93201</v>
+        <v>93404</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kulla, Kulla, Vb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>753603</v>
+        <v>753224</v>
       </c>
       <c r="R110" t="n">
-        <v>7095544</v>
+        <v>7095384</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12630,17 +12639,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga sågad, basen mot stående tall</t>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12655,24 +12669,24 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120533224</t>
+          <t>https://artportalen.se/Sighting/136713127</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120533225</v>
+        <v>120533224</v>
       </c>
       <c r="B111" t="n">
         <v>93201</v>
@@ -12707,10 +12721,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>753309</v>
+        <v>753603</v>
       </c>
       <c r="R111" t="n">
-        <v>7095549</v>
+        <v>7095544</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12747,7 +12761,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Under tunn talllåga i mossa</t>
+          <t>Under tunn talllåga sågad, basen mot stående tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12773,13 +12787,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120533225</t>
+          <t>https://artportalen.se/Sighting/120533224</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120533226</v>
+        <v>120533225</v>
       </c>
       <c r="B112" t="n">
         <v>93201</v>
@@ -12814,10 +12828,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>753301</v>
+        <v>753309</v>
       </c>
       <c r="R112" t="n">
-        <v>7095541</v>
+        <v>7095549</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12854,7 +12868,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Under tunn tallåga i grop</t>
+          <t>Under tunn talllåga i mossa</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12880,13 +12894,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120533226</t>
+          <t>https://artportalen.se/Sighting/120533225</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120533227</v>
+        <v>120533226</v>
       </c>
       <c r="B113" t="n">
         <v>93201</v>
@@ -12921,10 +12935,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>753299</v>
+        <v>753301</v>
       </c>
       <c r="R113" t="n">
-        <v>7095581</v>
+        <v>7095541</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12961,7 +12975,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Under tunn tallgren invid tall</t>
+          <t>Under tunn tallåga i grop</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12987,13 +13001,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120533227</t>
+          <t>https://artportalen.se/Sighting/120533226</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120533228</v>
+        <v>120533227</v>
       </c>
       <c r="B114" t="n">
         <v>93201</v>
@@ -13028,10 +13042,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>753100</v>
+        <v>753299</v>
       </c>
       <c r="R114" t="n">
-        <v>7095391</v>
+        <v>7095581</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13068,7 +13082,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Under tallåga i slänt</t>
+          <t>Under tunn tallgren invid tall</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13094,13 +13108,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120533228</t>
+          <t>https://artportalen.se/Sighting/120533227</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120533229</v>
+        <v>120533228</v>
       </c>
       <c r="B115" t="n">
         <v>93201</v>
@@ -13135,10 +13149,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>753282</v>
+        <v>753100</v>
       </c>
       <c r="R115" t="n">
-        <v>7095457</v>
+        <v>7095391</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13175,7 +13189,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Under längre tallåga vid stigen</t>
+          <t>Under tallåga i slänt</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13201,13 +13215,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120533229</t>
+          <t>https://artportalen.se/Sighting/120533228</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120533231</v>
+        <v>120533229</v>
       </c>
       <c r="B116" t="n">
         <v>93201</v>
@@ -13235,21 +13249,17 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>753358</v>
+        <v>753282</v>
       </c>
       <c r="R116" t="n">
-        <v>7095463</v>
+        <v>7095457</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13286,7 +13296,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Under tunn tallgren i mossa</t>
+          <t>Under längre tallåga vid stigen</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13312,13 +13322,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120533231</t>
+          <t>https://artportalen.se/Sighting/120533229</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120533232</v>
+        <v>120533231</v>
       </c>
       <c r="B117" t="n">
         <v>93201</v>
@@ -13348,7 +13358,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13357,10 +13367,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>753412</v>
+        <v>753358</v>
       </c>
       <c r="R117" t="n">
-        <v>7095506</v>
+        <v>7095463</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13397,7 +13407,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Under väldigt tunn tallåga</t>
+          <t>Under tunn tallgren i mossa</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13423,13 +13433,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120533232</t>
+          <t>https://artportalen.se/Sighting/120533231</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120676219</v>
+        <v>120533232</v>
       </c>
       <c r="B118" t="n">
         <v>93201</v>
@@ -13457,20 +13467,24 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Kullasjön, Kullasjön, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>753154</v>
+        <v>753412</v>
       </c>
       <c r="R118" t="n">
-        <v>7095555</v>
+        <v>7095506</v>
       </c>
       <c r="S118" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13494,22 +13508,17 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Under väldigt tunn tallåga</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13524,24 +13533,24 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120676219</t>
+          <t>https://artportalen.se/Sighting/120533232</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120676690</v>
+        <v>120676219</v>
       </c>
       <c r="B119" t="n">
         <v>93201</v>
@@ -13576,10 +13585,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>753287</v>
+        <v>753154</v>
       </c>
       <c r="R119" t="n">
-        <v>7095526</v>
+        <v>7095555</v>
       </c>
       <c r="S119" t="n">
         <v>1</v>
@@ -13611,7 +13620,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13621,7 +13630,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13647,13 +13656,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120676690</t>
+          <t>https://artportalen.se/Sighting/120676219</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120729360</v>
+        <v>120676690</v>
       </c>
       <c r="B120" t="n">
         <v>93201</v>
@@ -13684,17 +13693,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullasjön, Kullasjön, Vb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>753158</v>
+        <v>753287</v>
       </c>
       <c r="R120" t="n">
-        <v>7095546</v>
+        <v>7095526</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13721,14 +13730,19 @@
           <t>2024-10-26</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-10-26</t>
         </is>
       </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Under tallåga och tunn tallgren</t>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13743,24 +13757,24 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120729360</t>
+          <t>https://artportalen.se/Sighting/120676690</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120729361</v>
+        <v>120729360</v>
       </c>
       <c r="B121" t="n">
         <v>93201</v>
@@ -13795,10 +13809,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>753364</v>
+        <v>753158</v>
       </c>
       <c r="R121" t="n">
-        <v>7095622</v>
+        <v>7095546</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13835,7 +13849,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Under kolade vedrester</t>
+          <t>Under tallåga och tunn tallgren</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13861,13 +13875,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120729361</t>
+          <t>https://artportalen.se/Sighting/120729360</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120729362</v>
+        <v>120729361</v>
       </c>
       <c r="B122" t="n">
         <v>93201</v>
@@ -13902,10 +13916,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>753120</v>
+        <v>753364</v>
       </c>
       <c r="R122" t="n">
-        <v>7095733</v>
+        <v>7095622</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13942,7 +13956,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Under tunn tallåga, rest efter röjning</t>
+          <t>Under kolade vedrester</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13968,13 +13982,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120729362</t>
+          <t>https://artportalen.se/Sighting/120729361</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120729363</v>
+        <v>120729362</v>
       </c>
       <c r="B123" t="n">
         <v>93201</v>
@@ -14009,10 +14023,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>753361</v>
+        <v>753120</v>
       </c>
       <c r="R123" t="n">
-        <v>7095619</v>
+        <v>7095733</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14049,7 +14063,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Under tunn tallgren</t>
+          <t>Under tunn tallåga, rest efter röjning</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14075,13 +14089,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120729363</t>
+          <t>https://artportalen.se/Sighting/120729362</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120729364</v>
+        <v>120729363</v>
       </c>
       <c r="B124" t="n">
         <v>93201</v>
@@ -14109,21 +14123,17 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>753466</v>
+        <v>753361</v>
       </c>
       <c r="R124" t="n">
-        <v>7095627</v>
+        <v>7095619</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14160,7 +14170,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Under nedbruten tallåga, minst 10 fruktkroppar</t>
+          <t>Under tunn tallgren</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14186,13 +14196,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120729364</t>
+          <t>https://artportalen.se/Sighting/120729363</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128787962</v>
+        <v>120729364</v>
       </c>
       <c r="B125" t="n">
         <v>93201</v>
@@ -14220,20 +14230,24 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>753522</v>
+        <v>753466</v>
       </c>
       <c r="R125" t="n">
-        <v>7095689</v>
+        <v>7095627</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14257,17 +14271,17 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Under tunn tallåga, grenhög</t>
+          <t>Under nedbruten tallåga, minst 10 fruktkroppar</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14293,13 +14307,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787962</t>
+          <t>https://artportalen.se/Sighting/120729364</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128787963</v>
+        <v>128787962</v>
       </c>
       <c r="B126" t="n">
         <v>93201</v>
@@ -14334,10 +14348,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>753106</v>
+        <v>753522</v>
       </c>
       <c r="R126" t="n">
-        <v>7095389</v>
+        <v>7095689</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14364,17 +14378,17 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Under tunn tallåga, återfynd från 2024</t>
+          <t>Under tunn tallåga, grenhög</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14400,13 +14414,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787963</t>
+          <t>https://artportalen.se/Sighting/128787962</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128787965</v>
+        <v>128787963</v>
       </c>
       <c r="B127" t="n">
         <v>93201</v>
@@ -14441,10 +14455,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>753313</v>
+        <v>753106</v>
       </c>
       <c r="R127" t="n">
-        <v>7095539</v>
+        <v>7095389</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14471,17 +14485,17 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Under tunn tallgren, kapad</t>
+          <t>Under tunn tallåga, återfynd från 2024</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14507,13 +14521,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787965</t>
+          <t>https://artportalen.se/Sighting/128787963</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128937599</v>
+        <v>128787965</v>
       </c>
       <c r="B128" t="n">
         <v>93201</v>
@@ -14544,14 +14558,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>KåddisKulla, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>753174</v>
+        <v>753313</v>
       </c>
       <c r="R128" t="n">
-        <v>7095546</v>
+        <v>7095539</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14578,17 +14592,17 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Under tallåga</t>
+          <t>Under tunn tallgren, kapad</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14614,16 +14628,16 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128937599</t>
+          <t>https://artportalen.se/Sighting/128787965</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>136358182</v>
+        <v>128937599</v>
       </c>
       <c r="B129" t="n">
-        <v>93407</v>
+        <v>93201</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14651,14 +14665,14 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>KåddisKulla, Vb</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>753405</v>
+        <v>753174</v>
       </c>
       <c r="R129" t="n">
-        <v>7095481</v>
+        <v>7095546</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14685,17 +14699,17 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Under talllåga</t>
+          <t>Under tallåga</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14721,16 +14735,16 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136358182</t>
+          <t>https://artportalen.se/Sighting/128937599</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>136359040</v>
+        <v>136358182</v>
       </c>
       <c r="B130" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14758,14 +14772,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>753027</v>
+        <v>753405</v>
       </c>
       <c r="R130" t="n">
-        <v>7095391</v>
+        <v>7095481</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14802,7 +14816,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Under tunn talllåga i grop</t>
+          <t>Under talllåga</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14828,54 +14842,54 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136359040</t>
+          <t>https://artportalen.se/Sighting/136358182</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>103246127</v>
+        <v>136359040</v>
       </c>
       <c r="B131" t="n">
-        <v>93209</v>
+        <v>93408</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>753187</v>
+        <v>753027</v>
       </c>
       <c r="R131" t="n">
-        <v>7095610</v>
+        <v>7095391</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14899,12 +14913,17 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga i grop</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14919,24 +14938,24 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103246127</t>
+          <t>https://artportalen.se/Sighting/136359040</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>103246143</v>
+        <v>103246127</v>
       </c>
       <c r="B132" t="n">
         <v>93209</v>
@@ -14971,10 +14990,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>753599</v>
+        <v>753187</v>
       </c>
       <c r="R132" t="n">
-        <v>7095715</v>
+        <v>7095610</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15032,13 +15051,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103246143</t>
+          <t>https://artportalen.se/Sighting/103246127</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>103246145</v>
+        <v>103246143</v>
       </c>
       <c r="B133" t="n">
         <v>93209</v>
@@ -15073,10 +15092,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>753583</v>
+        <v>753599</v>
       </c>
       <c r="R133" t="n">
-        <v>7095639</v>
+        <v>7095715</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15134,13 +15153,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103246145</t>
+          <t>https://artportalen.se/Sighting/103246143</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>103246150</v>
+        <v>103246145</v>
       </c>
       <c r="B134" t="n">
         <v>93209</v>
@@ -15175,10 +15194,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>753454</v>
+        <v>753583</v>
       </c>
       <c r="R134" t="n">
-        <v>7095655</v>
+        <v>7095639</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15236,13 +15255,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103246150</t>
+          <t>https://artportalen.se/Sighting/103246145</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>103246159</v>
+        <v>103246150</v>
       </c>
       <c r="B135" t="n">
         <v>93209</v>
@@ -15277,10 +15296,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>753655</v>
+        <v>753454</v>
       </c>
       <c r="R135" t="n">
-        <v>7095473</v>
+        <v>7095655</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15338,13 +15357,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103246159</t>
+          <t>https://artportalen.se/Sighting/103246150</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>103246186</v>
+        <v>103246159</v>
       </c>
       <c r="B136" t="n">
         <v>93209</v>
@@ -15379,10 +15398,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>753179</v>
+        <v>753655</v>
       </c>
       <c r="R136" t="n">
-        <v>7095423</v>
+        <v>7095473</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15440,13 +15459,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103246186</t>
+          <t>https://artportalen.se/Sighting/103246159</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>103246187</v>
+        <v>103246186</v>
       </c>
       <c r="B137" t="n">
         <v>93209</v>
@@ -15481,10 +15500,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>753155</v>
+        <v>753179</v>
       </c>
       <c r="R137" t="n">
-        <v>7095402</v>
+        <v>7095423</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15542,13 +15561,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103246187</t>
+          <t>https://artportalen.se/Sighting/103246186</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>111642918</v>
+        <v>103246187</v>
       </c>
       <c r="B138" t="n">
         <v>93209</v>
@@ -15583,10 +15602,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>753146</v>
+        <v>753155</v>
       </c>
       <c r="R138" t="n">
-        <v>7095399</v>
+        <v>7095402</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15613,12 +15632,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15644,13 +15663,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111642918</t>
+          <t>https://artportalen.se/Sighting/103246187</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>111642919</v>
+        <v>111642918</v>
       </c>
       <c r="B139" t="n">
         <v>93209</v>
@@ -15685,10 +15704,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>752985</v>
+        <v>753146</v>
       </c>
       <c r="R139" t="n">
-        <v>7095181</v>
+        <v>7095399</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15746,13 +15765,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111642919</t>
+          <t>https://artportalen.se/Sighting/111642918</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120674846</v>
+        <v>111642919</v>
       </c>
       <c r="B140" t="n">
         <v>93209</v>
@@ -15783,17 +15802,17 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Kullasjön, Kullasjön, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>753008</v>
+        <v>752985</v>
       </c>
       <c r="R140" t="n">
-        <v>7095775</v>
+        <v>7095181</v>
       </c>
       <c r="S140" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15817,22 +15836,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>09:57</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>09:57</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15847,74 +15856,65 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120674846</t>
+          <t>https://artportalen.se/Sighting/111642919</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1667764</v>
+        <v>120674846</v>
       </c>
       <c r="B141" t="n">
-        <v>89055</v>
+        <v>93209</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4385</v>
+        <v>4366</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Broskvaxing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Gliophorus laetus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Pers.) Herink</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullasjön, Kullasjön, Vb</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>752989</v>
+        <v>753008</v>
       </c>
       <c r="R141" t="n">
-        <v>7095037</v>
+        <v>7095775</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15938,12 +15938,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2012-09-20</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2012-11-23</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15955,41 +15965,30 @@
       <c r="AG141" t="b">
         <v>0</v>
       </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>i gräsmattan</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>Nada Lipovac</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr"/>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1667764</t>
+          <t>https://artportalen.se/Sighting/120674846</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1197762</v>
+        <v>1667764</v>
       </c>
       <c r="B142" t="n">
-        <v>89029</v>
+        <v>89055</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15997,19 +15996,23 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4392</v>
+        <v>4385</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ängsvaxing agg.</t>
+          <t>Broskvaxing</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr"/>
+          <t>Gliophorus laetus</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Pers.) Herink</t>
+        </is>
+      </c>
       <c r="I142" t="inlineStr">
         <is>
           <t>1</t>
@@ -16026,10 +16029,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>752993</v>
+        <v>752989</v>
       </c>
       <c r="R142" t="n">
-        <v>7095055</v>
+        <v>7095037</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16078,6 +16081,12 @@
           <t>i gräsmattan</t>
         </is>
       </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr"/>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
@@ -16092,16 +16101,16 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1197762</t>
+          <t>https://artportalen.se/Sighting/1667764</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1226779</v>
+        <v>1197762</v>
       </c>
       <c r="B143" t="n">
-        <v>89106</v>
+        <v>89029</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16109,23 +16118,19 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4394</v>
+        <v>4392</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Ängsvaxing agg.</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kühner</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>1</t>
@@ -16142,10 +16147,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>752994</v>
+        <v>752993</v>
       </c>
       <c r="R143" t="n">
-        <v>7095033</v>
+        <v>7095055</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -16208,16 +16213,16 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1226779</t>
+          <t>https://artportalen.se/Sighting/1197762</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1256425</v>
+        <v>1226779</v>
       </c>
       <c r="B144" t="n">
-        <v>89035</v>
+        <v>89106</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16225,19 +16230,23 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4398</v>
+        <v>4394</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vitvaxing agg.</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr"/>
+          <t>Hygrocybe reidii</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kühner</t>
+        </is>
+      </c>
       <c r="I144" t="inlineStr">
         <is>
           <t>1</t>
@@ -16257,7 +16266,7 @@
         <v>752994</v>
       </c>
       <c r="R144" t="n">
-        <v>7095041</v>
+        <v>7095033</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -16306,12 +16315,6 @@
           <t>i gräsmattan</t>
         </is>
       </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>Nada Lipovac</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr"/>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
@@ -16326,54 +16329,59 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1256425</t>
+          <t>https://artportalen.se/Sighting/1226779</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>111642906</v>
+        <v>1256425</v>
       </c>
       <c r="B145" t="n">
-        <v>92841</v>
+        <v>89035</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4745</v>
+        <v>4398</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vitvaxing agg.</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>753163</v>
+        <v>752994</v>
       </c>
       <c r="R145" t="n">
-        <v>7095373</v>
+        <v>7095041</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16397,12 +16405,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2012-09-20</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2012-11-23</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16414,30 +16422,41 @@
       <c r="AG145" t="b">
         <v>0</v>
       </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>i gräsmattan</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr"/>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Nada Lipovac</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Nada Lipovac</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111642906</t>
+          <t>https://artportalen.se/Sighting/1256425</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128787985</v>
+        <v>111642906</v>
       </c>
       <c r="B146" t="n">
-        <v>90522</v>
+        <v>92841</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16445,41 +16464,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4962</v>
+        <v>4745</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>753179</v>
+        <v>753163</v>
       </c>
       <c r="R146" t="n">
-        <v>7095384</v>
+        <v>7095373</v>
       </c>
       <c r="S146" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16503,19 +16518,19 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG146" t="b">
         <v>0</v>
@@ -16523,65 +16538,69 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787985</t>
+          <t>https://artportalen.se/Sighting/111642906</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>110217658</v>
+        <v>128787985</v>
       </c>
       <c r="B147" t="n">
-        <v>92152</v>
+        <v>90522</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5260</v>
+        <v>4962</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Renvall</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>753107</v>
+        <v>753179</v>
       </c>
       <c r="R147" t="n">
-        <v>7095391</v>
+        <v>7095384</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16605,111 +16624,85 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AG147" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL147" t="inlineStr">
-        <is>
-          <t>Klen tallåga.</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Klen tallåga.</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr">
-        <is>
-          <t>Gudrun Norstedt</t>
-        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110217658</t>
+          <t>https://artportalen.se/Sighting/128787985</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>136356211</v>
+        <v>110217658</v>
       </c>
       <c r="B148" t="n">
-        <v>93432</v>
+        <v>92152</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5449</v>
+        <v>5260</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr"/>
+          <t>Postia lateritia</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Renvall</t>
+        </is>
+      </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>753106</v>
+        <v>753107</v>
       </c>
       <c r="R148" t="n">
-        <v>7095389</v>
+        <v>7095391</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16733,17 +16726,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Delvis under talllåga</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16752,33 +16740,63 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>Klen tallåga.</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Klen tallåga.</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136356211</t>
+          <t>https://artportalen.se/Sighting/110217658</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>136357506</v>
+        <v>136356211</v>
       </c>
       <c r="B149" t="n">
-        <v>93432</v>
+        <v>93433</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16802,14 +16820,14 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>753121</v>
+        <v>753106</v>
       </c>
       <c r="R149" t="n">
-        <v>7095419</v>
+        <v>7095389</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -16844,6 +16862,11 @@
           <t>2026-09-05</t>
         </is>
       </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Delvis under talllåga</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
@@ -16867,16 +16890,16 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136357506</t>
+          <t>https://artportalen.se/Sighting/136356211</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>136358191</v>
+        <v>136357506</v>
       </c>
       <c r="B150" t="n">
-        <v>93432</v>
+        <v>93433</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16904,10 +16927,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>753405</v>
+        <v>753121</v>
       </c>
       <c r="R150" t="n">
-        <v>7095481</v>
+        <v>7095419</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -16942,11 +16965,6 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Under talllåga, med smalfotad taggsvamp</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -16970,54 +16988,50 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136358191</t>
+          <t>https://artportalen.se/Sighting/136357506</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>136665866</v>
+        <v>136358191</v>
       </c>
       <c r="B151" t="n">
-        <v>92771</v>
+        <v>93433</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5454</v>
+        <v>5449</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>753616</v>
+        <v>753405</v>
       </c>
       <c r="R151" t="n">
-        <v>7095666</v>
+        <v>7095481</v>
       </c>
       <c r="S151" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17041,22 +17055,17 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>10:39</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>10:39</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Under talllåga, med smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17071,27 +17080,27 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136665866</t>
+          <t>https://artportalen.se/Sighting/136358191</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120533239</v>
+        <v>136665866</v>
       </c>
       <c r="B152" t="n">
-        <v>93235</v>
+        <v>92772</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17099,41 +17108,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5966</v>
+        <v>5454</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>752996</v>
+        <v>753616</v>
       </c>
       <c r="R152" t="n">
-        <v>7095304</v>
+        <v>7095666</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17157,12 +17162,22 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17177,24 +17192,24 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120533239</t>
+          <t>https://artportalen.se/Sighting/136665866</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120533241</v>
+        <v>120533239</v>
       </c>
       <c r="B153" t="n">
         <v>93235</v>
@@ -17222,17 +17237,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>753412</v>
+        <v>752996</v>
       </c>
       <c r="R153" t="n">
-        <v>7095620</v>
+        <v>7095304</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17290,13 +17309,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120533241</t>
+          <t>https://artportalen.se/Sighting/120533239</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120673249</v>
+        <v>120533241</v>
       </c>
       <c r="B154" t="n">
         <v>93235</v>
@@ -17327,17 +17346,17 @@
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Kullasjön, Kullasjön, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>752963</v>
+        <v>753412</v>
       </c>
       <c r="R154" t="n">
-        <v>7095347</v>
+        <v>7095620</v>
       </c>
       <c r="S154" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17361,22 +17380,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>08:11</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>08:11</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17391,24 +17400,24 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120673249</t>
+          <t>https://artportalen.se/Sighting/120533241</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120673747</v>
+        <v>120673249</v>
       </c>
       <c r="B155" t="n">
         <v>93235</v>
@@ -17443,10 +17452,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>752950</v>
+        <v>752963</v>
       </c>
       <c r="R155" t="n">
-        <v>7095623</v>
+        <v>7095347</v>
       </c>
       <c r="S155" t="n">
         <v>1</v>
@@ -17478,7 +17487,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17488,7 +17497,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17514,13 +17523,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120673747</t>
+          <t>https://artportalen.se/Sighting/120673249</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120675378</v>
+        <v>120673747</v>
       </c>
       <c r="B156" t="n">
         <v>93235</v>
@@ -17555,10 +17564,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>753101</v>
+        <v>752950</v>
       </c>
       <c r="R156" t="n">
-        <v>7095680</v>
+        <v>7095623</v>
       </c>
       <c r="S156" t="n">
         <v>1</v>
@@ -17590,7 +17599,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17600,7 +17609,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17626,13 +17635,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120675378</t>
+          <t>https://artportalen.se/Sighting/120673747</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120675392</v>
+        <v>120675378</v>
       </c>
       <c r="B157" t="n">
         <v>93235</v>
@@ -17667,10 +17676,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>753058</v>
+        <v>753101</v>
       </c>
       <c r="R157" t="n">
-        <v>7095597</v>
+        <v>7095680</v>
       </c>
       <c r="S157" t="n">
         <v>1</v>
@@ -17702,7 +17711,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17712,7 +17721,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17738,13 +17747,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120675392</t>
+          <t>https://artportalen.se/Sighting/120675378</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120677239</v>
+        <v>120675392</v>
       </c>
       <c r="B158" t="n">
         <v>93235</v>
@@ -17779,10 +17788,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>753407</v>
+        <v>753058</v>
       </c>
       <c r="R158" t="n">
-        <v>7095629</v>
+        <v>7095597</v>
       </c>
       <c r="S158" t="n">
         <v>1</v>
@@ -17814,7 +17823,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17824,7 +17833,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17850,13 +17859,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120677239</t>
+          <t>https://artportalen.se/Sighting/120675392</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120729371</v>
+        <v>120677239</v>
       </c>
       <c r="B159" t="n">
         <v>93235</v>
@@ -17884,24 +17893,20 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullasjön, Kullasjön, Vb</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>752990</v>
+        <v>753407</v>
       </c>
       <c r="R159" t="n">
-        <v>7095781</v>
+        <v>7095629</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17928,9 +17933,19 @@
           <t>2024-10-26</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17945,66 +17960,66 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120729371</t>
+          <t>https://artportalen.se/Sighting/120677239</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120533222</v>
+        <v>120729371</v>
       </c>
       <c r="B160" t="n">
-        <v>93181</v>
+        <v>93235</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6055</v>
+        <v>5966</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>753304</v>
+        <v>752990</v>
       </c>
       <c r="R160" t="n">
-        <v>7095588</v>
+        <v>7095781</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18031,17 +18046,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Cirka 20 fk under nedbruten talllåga vid grop</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18067,13 +18077,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120533222</t>
+          <t>https://artportalen.se/Sighting/120729371</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128761110</v>
+        <v>120533222</v>
       </c>
       <c r="B161" t="n">
         <v>93181</v>
@@ -18101,20 +18111,24 @@
           <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>753440</v>
+        <v>753304</v>
       </c>
       <c r="R161" t="n">
-        <v>7095719</v>
+        <v>7095588</v>
       </c>
       <c r="S161" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18138,17 +18152,17 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Under mindre tallgren, lav och mossor som msrkskikt</t>
+          <t>Cirka 20 fk under nedbruten talllåga vid grop</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18174,16 +18188,16 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128761110</t>
+          <t>https://artportalen.se/Sighting/120533222</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>136358859</v>
+        <v>128761110</v>
       </c>
       <c r="B162" t="n">
-        <v>93387</v>
+        <v>93181</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18215,10 +18229,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>753167</v>
+        <v>753440</v>
       </c>
       <c r="R162" t="n">
-        <v>7095382</v>
+        <v>7095719</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -18245,12 +18259,17 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Under mindre tallgren, lav och mossor som msrkskikt</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18276,16 +18295,16 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136358859</t>
+          <t>https://artportalen.se/Sighting/128761110</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>136583701</v>
+        <v>136358859</v>
       </c>
       <c r="B163" t="n">
-        <v>93387</v>
+        <v>93388</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18313,14 +18332,14 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Kullasjön O om, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>753303</v>
+        <v>753167</v>
       </c>
       <c r="R163" t="n">
-        <v>7095583</v>
+        <v>7095382</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -18347,22 +18366,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18377,27 +18386,27 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Gunnar Janson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Gunnar Janson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136583701</t>
+          <t>https://artportalen.se/Sighting/136358859</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>102974116</v>
+        <v>136583701</v>
       </c>
       <c r="B164" t="n">
-        <v>90691</v>
+        <v>93388</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18405,48 +18414,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6276</v>
+        <v>6055</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Piparböle, Vb</t>
+          <t>Kullasjön O om, Vb</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>753549</v>
+        <v>753303</v>
       </c>
       <c r="R164" t="n">
-        <v>7095510</v>
+        <v>7095583</v>
       </c>
       <c r="S164" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18470,22 +18468,22 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18494,36 +18492,30 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Helena Strandberg</t>
+          <t>Gunnar Janson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Helena Strandberg</t>
+          <t>Gunnar Janson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102974116</t>
+          <t>https://artportalen.se/Sighting/136583701</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>103246131</v>
+        <v>102974116</v>
       </c>
       <c r="B165" t="n">
         <v>90691</v>
@@ -18551,20 +18543,31 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Piparböle, Vb</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>753383</v>
+        <v>753549</v>
       </c>
       <c r="R165" t="n">
-        <v>7095695</v>
+        <v>7095510</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18588,12 +18591,22 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18602,30 +18615,36 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Helena Strandberg</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Helena Strandberg</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103246131</t>
+          <t>https://artportalen.se/Sighting/102974116</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>103246146</v>
+        <v>103246131</v>
       </c>
       <c r="B166" t="n">
         <v>90691</v>
@@ -18660,10 +18679,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>753552</v>
+        <v>753383</v>
       </c>
       <c r="R166" t="n">
-        <v>7095625</v>
+        <v>7095695</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18721,13 +18740,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103246146</t>
+          <t>https://artportalen.se/Sighting/103246131</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>103246152</v>
+        <v>103246146</v>
       </c>
       <c r="B167" t="n">
         <v>90691</v>
@@ -18762,10 +18781,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>753489</v>
+        <v>753552</v>
       </c>
       <c r="R167" t="n">
-        <v>7095588</v>
+        <v>7095625</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18823,13 +18842,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103246152</t>
+          <t>https://artportalen.se/Sighting/103246146</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>103246154</v>
+        <v>103246152</v>
       </c>
       <c r="B168" t="n">
         <v>90691</v>
@@ -18864,10 +18883,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>753533</v>
+        <v>753489</v>
       </c>
       <c r="R168" t="n">
-        <v>7095559</v>
+        <v>7095588</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18925,13 +18944,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103246154</t>
+          <t>https://artportalen.se/Sighting/103246152</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>103246188</v>
+        <v>103246154</v>
       </c>
       <c r="B169" t="n">
         <v>90691</v>
@@ -18966,10 +18985,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>753095</v>
+        <v>753533</v>
       </c>
       <c r="R169" t="n">
-        <v>7095382</v>
+        <v>7095559</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19027,13 +19046,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103246188</t>
+          <t>https://artportalen.se/Sighting/103246154</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>103549610</v>
+        <v>103246188</v>
       </c>
       <c r="B170" t="n">
         <v>90691</v>
@@ -19064,14 +19083,14 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Kullaheden, Piparböle, Umeå, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>753538</v>
+        <v>753095</v>
       </c>
       <c r="R170" t="n">
-        <v>7095438</v>
+        <v>7095382</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19098,12 +19117,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19118,24 +19137,24 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Carl Jansson, Andreas Estensen</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103549610</t>
+          <t>https://artportalen.se/Sighting/103246188</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>111642933</v>
+        <v>103549610</v>
       </c>
       <c r="B171" t="n">
         <v>90691</v>
@@ -19166,14 +19185,14 @@
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kullaheden, Piparböle, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>753501</v>
+        <v>753538</v>
       </c>
       <c r="R171" t="n">
-        <v>7095437</v>
+        <v>7095438</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19200,12 +19219,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19220,24 +19239,24 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson, Andreas Estensen</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111642933</t>
+          <t>https://artportalen.se/Sighting/103549610</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>111642934</v>
+        <v>111642933</v>
       </c>
       <c r="B172" t="n">
         <v>90691</v>
@@ -19272,10 +19291,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>753425</v>
+        <v>753501</v>
       </c>
       <c r="R172" t="n">
-        <v>7095407</v>
+        <v>7095437</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19333,13 +19352,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111642934</t>
+          <t>https://artportalen.se/Sighting/111642933</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>112013672</v>
+        <v>111642934</v>
       </c>
       <c r="B173" t="n">
         <v>90691</v>
@@ -19370,17 +19389,17 @@
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>753149</v>
+        <v>753425</v>
       </c>
       <c r="R173" t="n">
-        <v>7095358</v>
+        <v>7095407</v>
       </c>
       <c r="S173" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19404,22 +19423,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>20:02</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>20:02</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19434,24 +19443,24 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Louise Almén, Britta Sterner</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112013672</t>
+          <t>https://artportalen.se/Sighting/111642934</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119587687</v>
+        <v>112013672</v>
       </c>
       <c r="B174" t="n">
         <v>90691</v>
@@ -19480,19 +19489,16 @@
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Hedarna, Kulla, Hedarna, Kulla, Vb</t>
+          <t>Kullabäcken, Vb</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>753174</v>
+        <v>753149</v>
       </c>
       <c r="R174" t="n">
-        <v>7095438</v>
+        <v>7095358</v>
       </c>
       <c r="S174" t="n">
         <v>25</v>
@@ -19519,22 +19525,22 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19543,39 +19549,33 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Erik Persson, Lovisa Åberg Persson</t>
+          <t>Isak Vahlström, Louise Almén, Britta Sterner</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119587687</t>
+          <t>https://artportalen.se/Sighting/112013672</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>103549603</v>
+        <v>119587687</v>
       </c>
       <c r="B175" t="n">
-        <v>90710</v>
+        <v>90691</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19583,21 +19583,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19606,17 +19606,17 @@
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Kullaheden, Piparböle, Umeå, Vb</t>
+          <t>Hedarna, Kulla, Hedarna, Kulla, Vb</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>753311</v>
+        <v>753174</v>
       </c>
       <c r="R175" t="n">
-        <v>7095545</v>
+        <v>7095438</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19640,17 +19640,22 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Sporer 5,8-6,9 x 3,4-4,6 μm</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19659,35 +19664,36 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Erik Persson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Carl Jansson, Andreas Estensen</t>
+          <t>Erik Persson, Lovisa Åberg Persson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103549603</t>
+          <t>https://artportalen.se/Sighting/119587687</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128787941</v>
+        <v>103549603</v>
       </c>
       <c r="B176" t="n">
         <v>90710</v>
@@ -19715,24 +19721,23 @@
           <t>(Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullaheden, Piparböle, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>753398</v>
+        <v>753311</v>
       </c>
       <c r="R176" t="n">
-        <v>7095650</v>
+        <v>7095545</v>
       </c>
       <c r="S176" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19756,12 +19761,17 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Sporer 5,8-6,9 x 3,4-4,6 μm</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19769,6 +19779,11 @@
       </c>
       <c r="AE176" t="b">
         <v>0</v>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG176" t="b">
         <v>0</v>
@@ -19776,70 +19791,69 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson, Andreas Estensen</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787941</t>
+          <t>https://artportalen.se/Sighting/103549603</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>120533219</v>
+        <v>128787941</v>
       </c>
       <c r="B177" t="n">
-        <v>57950</v>
+        <v>90710</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100049</v>
+        <v>6286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>753126</v>
+        <v>753398</v>
       </c>
       <c r="R177" t="n">
-        <v>7095398</v>
+        <v>7095650</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19863,17 +19877,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Äldre födohack</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19884,26 +19893,6 @@
       </c>
       <c r="AG177" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL177" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallhögstubbe</t>
-        </is>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
@@ -19919,13 +19908,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120533219</t>
+          <t>https://artportalen.se/Sighting/128787941</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120533220</v>
+        <v>120533219</v>
       </c>
       <c r="B178" t="n">
         <v>57950</v>
@@ -19965,10 +19954,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>753443</v>
+        <v>753126</v>
       </c>
       <c r="R178" t="n">
-        <v>7095503</v>
+        <v>7095398</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20051,13 +20040,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120533220</t>
+          <t>https://artportalen.se/Sighting/120533219</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120533221</v>
+        <v>120533220</v>
       </c>
       <c r="B179" t="n">
         <v>57950</v>
@@ -20097,10 +20086,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>753310</v>
+        <v>753443</v>
       </c>
       <c r="R179" t="n">
-        <v>7095459</v>
+        <v>7095503</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20183,13 +20172,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120533221</t>
+          <t>https://artportalen.se/Sighting/120533220</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120673729</v>
+        <v>120533221</v>
       </c>
       <c r="B180" t="n">
         <v>57950</v>
@@ -20218,19 +20207,24 @@
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Kullasjön, Kullasjön, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>752953</v>
+        <v>753310</v>
       </c>
       <c r="R180" t="n">
-        <v>7095627</v>
+        <v>7095459</v>
       </c>
       <c r="S180" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20254,27 +20248,17 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>08:57</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>08:57</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Gammalt spår</t>
+          <t>Äldre födohack</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20285,28 +20269,48 @@
       </c>
       <c r="AG180" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL180" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallhögstubbe</t>
+        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120673729</t>
+          <t>https://artportalen.se/Sighting/120533221</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120729356</v>
+        <v>120673729</v>
       </c>
       <c r="B181" t="n">
         <v>57950</v>
@@ -20335,24 +20339,19 @@
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullasjön, Kullasjön, Vb</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>753284</v>
+        <v>752953</v>
       </c>
       <c r="R181" t="n">
-        <v>7095591</v>
+        <v>7095627</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20379,14 +20378,24 @@
           <t>2024-10-26</t>
         </is>
       </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2024-10-26</t>
         </is>
       </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Tallåga</t>
+          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20397,43 +20406,28 @@
       </c>
       <c r="AG181" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120729356</t>
+          <t>https://artportalen.se/Sighting/120673729</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120729357</v>
+        <v>120729356</v>
       </c>
       <c r="B182" t="n">
         <v>57950</v>
@@ -20473,10 +20467,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>753150</v>
+        <v>753284</v>
       </c>
       <c r="R182" t="n">
-        <v>7095606</v>
+        <v>7095591</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20513,7 +20507,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Tallhögstubbe, silverfura</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20554,13 +20548,13 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120729357</t>
+          <t>https://artportalen.se/Sighting/120729356</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120729358</v>
+        <v>120729357</v>
       </c>
       <c r="B183" t="n">
         <v>57950</v>
@@ -20600,10 +20594,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>753149</v>
+        <v>753150</v>
       </c>
       <c r="R183" t="n">
-        <v>7095555</v>
+        <v>7095606</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20640,7 +20634,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Tallhögstubbe</t>
+          <t>Tallhögstubbe, silverfura</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20681,13 +20675,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120729358</t>
+          <t>https://artportalen.se/Sighting/120729357</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120729359</v>
+        <v>120729358</v>
       </c>
       <c r="B184" t="n">
         <v>57950</v>
@@ -20727,10 +20721,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>752966</v>
+        <v>753149</v>
       </c>
       <c r="R184" t="n">
-        <v>7095719</v>
+        <v>7095555</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20808,33 +20802,33 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120729359</t>
+          <t>https://artportalen.se/Sighting/120729358</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>103549599</v>
+        <v>120729359</v>
       </c>
       <c r="B185" t="n">
-        <v>57794</v>
+        <v>57950</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>102621</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -20845,19 +20839,19 @@
       <c r="I185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Kullaheden, Piparböle, Umeå, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>753226</v>
+        <v>752966</v>
       </c>
       <c r="R185" t="n">
-        <v>7095373</v>
+        <v>7095719</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20884,12 +20878,17 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20900,48 +20899,63 @@
       </c>
       <c r="AG185" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Carl Jansson, Andreas Estensen</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103549599</t>
+          <t>https://artportalen.se/Sighting/120729359</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120729372</v>
+        <v>103549599</v>
       </c>
       <c r="B186" t="n">
-        <v>58327</v>
+        <v>57794</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>103015</v>
+        <v>102621</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -20950,24 +20964,21 @@
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullaheden, Piparböle, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>753084</v>
+        <v>753226</v>
       </c>
       <c r="R186" t="n">
-        <v>7095717</v>
+        <v>7095373</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20994,12 +21005,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21014,24 +21025,24 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson, Andreas Estensen</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120729372</t>
+          <t>https://artportalen.se/Sighting/103549599</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120729373</v>
+        <v>120729372</v>
       </c>
       <c r="B187" t="n">
         <v>58327</v>
@@ -21074,10 +21085,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>752990</v>
+        <v>753084</v>
       </c>
       <c r="R187" t="n">
-        <v>7095436</v>
+        <v>7095717</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21135,54 +21146,62 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120729373</t>
+          <t>https://artportalen.se/Sighting/120729372</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120673188</v>
+        <v>120729373</v>
       </c>
       <c r="B188" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Kullasjön, Umeå, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>752983</v>
+        <v>752990</v>
       </c>
       <c r="R188" t="n">
-        <v>7095311</v>
+        <v>7095436</v>
       </c>
       <c r="S188" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21209,19 +21228,9 @@
           <t>2024-10-26</t>
         </is>
       </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>08:00</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21236,24 +21245,24 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120673188</t>
+          <t>https://artportalen.se/Sighting/120729373</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120675156</v>
+        <v>120673188</v>
       </c>
       <c r="B189" t="n">
         <v>58114</v>
@@ -21284,14 +21293,14 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Kullasjön, Kullasjön, Vb</t>
+          <t>Kullasjön, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>753053</v>
+        <v>752983</v>
       </c>
       <c r="R189" t="n">
-        <v>7095698</v>
+        <v>7095311</v>
       </c>
       <c r="S189" t="n">
         <v>1</v>
@@ -21323,7 +21332,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -21333,7 +21342,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21359,13 +21368,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120675156</t>
+          <t>https://artportalen.se/Sighting/120673188</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>120676556</v>
+        <v>120675156</v>
       </c>
       <c r="B190" t="n">
         <v>58114</v>
@@ -21396,14 +21405,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Kullabäcken (övre), Umeå, Vb</t>
+          <t>Kullasjön, Kullasjön, Vb</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>753289</v>
+        <v>753053</v>
       </c>
       <c r="R190" t="n">
-        <v>7095518</v>
+        <v>7095698</v>
       </c>
       <c r="S190" t="n">
         <v>1</v>
@@ -21435,7 +21444,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21445,7 +21454,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21471,13 +21480,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120676556</t>
+          <t>https://artportalen.se/Sighting/120675156</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>120692477</v>
+        <v>120676556</v>
       </c>
       <c r="B191" t="n">
         <v>58114</v>
@@ -21505,32 +21514,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kullabäcken (övre), Umeå, Vb</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>753191</v>
+        <v>753289</v>
       </c>
       <c r="R191" t="n">
-        <v>7095559</v>
+        <v>7095518</v>
       </c>
       <c r="S191" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -21559,7 +21556,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21569,7 +21566,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21584,24 +21581,24 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120692477</t>
+          <t>https://artportalen.se/Sighting/120676556</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127074261</v>
+        <v>120692477</v>
       </c>
       <c r="B192" t="n">
         <v>58114</v>
@@ -21634,21 +21631,24 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>753293</v>
+        <v>753191</v>
       </c>
       <c r="R192" t="n">
-        <v>7095457</v>
+        <v>7095559</v>
       </c>
       <c r="S192" t="n">
         <v>50</v>
@@ -21675,22 +21675,22 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21716,13 +21716,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127074261</t>
+          <t>https://artportalen.se/Sighting/120692477</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128464803</v>
+        <v>127074261</v>
       </c>
       <c r="B193" t="n">
         <v>58114</v>
@@ -21755,27 +21755,24 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>753527</v>
+        <v>753293</v>
       </c>
       <c r="R193" t="n">
-        <v>7095601</v>
+        <v>7095457</v>
       </c>
       <c r="S193" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21799,22 +21796,22 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21840,13 +21837,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128464803</t>
+          <t>https://artportalen.se/Sighting/127074261</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128787986</v>
+        <v>128464803</v>
       </c>
       <c r="B194" t="n">
         <v>58114</v>
@@ -21874,7 +21871,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr">
@@ -21889,10 +21890,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>753392</v>
+        <v>753527</v>
       </c>
       <c r="R194" t="n">
-        <v>7095478</v>
+        <v>7095601</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -21919,22 +21920,22 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21960,56 +21961,59 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128787986</t>
+          <t>https://artportalen.se/Sighting/128464803</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>136357484</v>
+        <v>128787986</v>
       </c>
       <c r="B195" t="n">
-        <v>106475</v>
+        <v>58114</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220827</v>
+        <v>103021</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tallört (aggregat)</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Monotropa hypopitys agg.</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Kullaheden, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>753121</v>
+        <v>753392</v>
       </c>
       <c r="R195" t="n">
-        <v>7095419</v>
+        <v>7095478</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -22036,12 +22040,22 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22067,51 +22081,56 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136357484</t>
+          <t>https://artportalen.se/Sighting/128787986</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>136358853</v>
+        <v>136357484</v>
       </c>
       <c r="B196" t="n">
-        <v>93434</v>
+        <v>106476</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>232140</v>
+        <v>220827</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Tallört (aggregat)</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>Monotropa hypopitys agg.</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>753167</v>
+        <v>753121</v>
       </c>
       <c r="R196" t="n">
-        <v>7095382</v>
+        <v>7095419</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -22146,11 +22165,6 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>Under äldre tallåga. Även spadskinn. Båda globalt rödlistade VU</t>
-        </is>
-      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
@@ -22174,38 +22188,38 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136358853</t>
+          <t>https://artportalen.se/Sighting/136357484</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119718999</v>
+        <v>136358853</v>
       </c>
       <c r="B197" t="n">
-        <v>92328</v>
+        <v>93435</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6040162</v>
+        <v>232140</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -22215,13 +22229,13 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>753545</v>
+        <v>753167</v>
       </c>
       <c r="R197" t="n">
-        <v>7095797</v>
+        <v>7095382</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -22245,12 +22259,17 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Under äldre tallåga. Även spadskinn. Båda globalt rödlistade VU</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22265,27 +22284,27 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718999</t>
+          <t>https://artportalen.se/Sighting/136358853</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119587677</v>
+        <v>119718999</v>
       </c>
       <c r="B198" t="n">
-        <v>93218</v>
+        <v>92328</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22293,35 +22312,37 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6331648</v>
+        <v>6040162</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Phellodon aquiloniniger</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>A.M.Ainsw. &amp; Svantesson</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Hedarna, Kulla, Hedarna, Kulla, Vb</t>
+          <t>Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>753229</v>
+        <v>753545</v>
       </c>
       <c r="R198" t="n">
-        <v>7095443</v>
+        <v>7095797</v>
       </c>
       <c r="S198" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -22345,27 +22366,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>18:17</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>Ändrad från P. niger efter nya beskrivningar av arter i gruppen. Detta fynd i sandtallskog. Beskrivningar i "The genus Phellodon (Thelephorales, Basidiomycota) in Europe: Four new species, one new combination, four new typifications and a first European record" (Svantesson et al, 2024).</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22374,86 +22380,69 @@
       <c r="AE198" t="b">
         <v>0</v>
       </c>
-      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Erik Persson, Lovisa Åberg Persson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119587677</t>
+          <t>https://artportalen.se/Sighting/119718999</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1718088</v>
+        <v>119587677</v>
       </c>
       <c r="B199" t="n">
-        <v>83322</v>
+        <v>93218</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4196</v>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>Fjällig jordtunga</t>
-        </is>
+        <v>6331648</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Geoglossum fallax</t>
+          <t>Phellodon aquiloniniger</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>E.J.Durand</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Hedarna, Kulla, Hedarna, Kulla, Vb</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>753004</v>
+        <v>753229</v>
       </c>
       <c r="R199" t="n">
-        <v>7094990</v>
+        <v>7095443</v>
       </c>
       <c r="S199" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -22477,12 +22466,27 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2012-09-20</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2012-11-23</t>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>Ändrad från P. niger efter nya beskrivningar av arter i gruppen. Detta fynd i sandtallskog. Beskrivningar i "The genus Phellodon (Thelephorales, Basidiomycota) in Europe: Four new species, one new combination, four new typifications and a first European record" (Svantesson et al, 2024).</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22491,44 +22495,39 @@
       <c r="AE199" t="b">
         <v>0</v>
       </c>
+      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>i gräsmattan</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>Nada Lipovac</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr"/>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Erik Persson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Erik Persson, Lovisa Åberg Persson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1718088</t>
+          <t>https://artportalen.se/Sighting/119587677</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>1736026</v>
+        <v>1718088</v>
       </c>
       <c r="B200" t="n">
-        <v>83330</v>
+        <v>83322</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22536,21 +22535,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4202</v>
+        <v>4196</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Fjällig jordtunga</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Geoglossum umbratile</t>
+          <t>Geoglossum fallax</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Sacc.</t>
+          <t>E.J.Durand</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -22569,10 +22568,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>752996</v>
+        <v>753004</v>
       </c>
       <c r="R200" t="n">
-        <v>7095002</v>
+        <v>7094990</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -22599,7 +22598,7 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2012-09-22</t>
+          <t>2012-09-20</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22618,7 +22617,7 @@
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>i gräsmattan, vidskogsvägen</t>
+          <t>i gräsmattan</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
@@ -22641,51 +22640,57 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1736026</t>
+          <t>https://artportalen.se/Sighting/1718088</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119682500</v>
+        <v>1736026</v>
       </c>
       <c r="B201" t="n">
-        <v>93201</v>
+        <v>83330</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4365</v>
+        <v>4202</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Geoglossum umbratile</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
+          <t>Sacc.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Kulla, Kulla, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>752918</v>
+        <v>752996</v>
       </c>
       <c r="R201" t="n">
         <v>7095002</v>
@@ -22715,22 +22720,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2012-09-22</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2012-11-23</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22739,78 +22734,82 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
-      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>i gräsmattan, vidskogsvägen</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr"/>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Anna Johansson</t>
+          <t>Nada Lipovac</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Anna Johansson, Sebastian Lennestig, Gabriella Toresson, Lina Albertsen, Anna Lindberg</t>
+          <t>Nada Lipovac</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119682500</t>
+          <t>https://artportalen.se/Sighting/1736026</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1298981</v>
+        <v>119682500</v>
       </c>
       <c r="B202" t="n">
-        <v>89080</v>
+        <v>93201</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4373</v>
+        <v>4365</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Sprödvaxing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hygrocybe ceracea</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Wulfen) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Kulla, Vb</t>
+          <t>Kulla, Kulla, Vb</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>753000</v>
+        <v>752918</v>
       </c>
       <c r="R202" t="n">
-        <v>7094997</v>
+        <v>7095002</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -22837,12 +22836,22 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2012-09-20</t>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2012-11-23</t>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22851,44 +22860,34 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
+      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>i gräsmattan</t>
-        </is>
-      </c>
-      <c r="AQ202" t="inlineStr">
-        <is>
-          <t>Nada Lipovac</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr"/>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Anna Johansson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Nada Lipovac</t>
+          <t>Anna Johansson, Sebastian Lennestig, Gabriella Toresson, Lina Albertsen, Anna Lindberg</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1298981</t>
+          <t>https://artportalen.se/Sighting/119682500</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127009098</v>
+        <v>1298981</v>
       </c>
       <c r="B203" t="n">
-        <v>58790</v>
+        <v>89080</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22896,21 +22895,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>208245</v>
+        <v>4373</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Sprödvaxing</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hygrocybe ceracea</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen) P.Kumm.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -22918,32 +22917,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>trafikdödad</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr"/>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Lustigkullaängen, Umeå, Vb</t>
+          <t>Kulla, Vb</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>752974</v>
+        <v>753000</v>
       </c>
       <c r="R203" t="n">
-        <v>7095000</v>
+        <v>7094997</v>
       </c>
       <c r="S203" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22967,22 +22958,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2012-09-20</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2012-11-23</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22991,34 +22972,44 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
-      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>i gräsmattan</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>Nada Lipovac</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr"/>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Bertil Brånin</t>
+          <t>Nada Lipovac</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Bertil Brånin</t>
+          <t>Nada Lipovac</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127009098</t>
+          <t>https://artportalen.se/Sighting/1298981</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>126953776</v>
+        <v>127009098</v>
       </c>
       <c r="B204" t="n">
-        <v>56905</v>
+        <v>58790</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23026,16 +23017,16 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>208260</v>
+        <v>208245</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -23097,27 +23088,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Mörk med tydligt zig zag band - 72 cm.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23144,56 +23130,57 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126953776</t>
+          <t>https://artportalen.se/Sighting/127009098</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>111773558</v>
+        <v>126953776</v>
       </c>
       <c r="B205" t="n">
-        <v>108201</v>
+        <v>56905</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>220107</v>
+        <v>208260</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
       <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
@@ -23231,12 +23218,27 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Mörk med tydligt zig zag band - 72 cm.</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23262,6 +23264,125 @@
       </c>
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126953776</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>111773558</v>
+      </c>
+      <c r="B206" t="n">
+        <v>108201</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Lustigkullaängen, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>752974</v>
+      </c>
+      <c r="R206" t="n">
+        <v>7095000</v>
+      </c>
+      <c r="S206" t="n">
+        <v>50</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF206" t="inlineStr"/>
+      <c r="AG206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Bertil Brånin</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>Bertil Brånin</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111773558</t>
         </is>
@@ -23473,6 +23594,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -1733,7 +1733,7 @@
         <v>136722796</v>
       </c>
       <c r="B11" t="n">
-        <v>90844</v>
+        <v>90846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>136723714</v>
       </c>
       <c r="B12" t="n">
-        <v>90844</v>
+        <v>90846</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136778053</v>
       </c>
       <c r="B21" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>136778057</v>
       </c>
       <c r="B22" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136778064</v>
       </c>
       <c r="B23" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136778066</v>
       </c>
       <c r="B24" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136811248</v>
       </c>
       <c r="B25" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>136356702</v>
       </c>
       <c r="B49" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>136356995</v>
       </c>
       <c r="B63" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>136455202</v>
       </c>
       <c r="B64" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136665861</v>
       </c>
       <c r="B65" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>136356269</v>
       </c>
       <c r="B106" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136356315</v>
       </c>
       <c r="B107" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>136356351</v>
       </c>
       <c r="B108" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>136356430</v>
       </c>
       <c r="B109" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>136357307</v>
       </c>
       <c r="B110" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>136357556</v>
       </c>
       <c r="B111" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>136358081</v>
       </c>
       <c r="B112" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>136455012</v>
       </c>
       <c r="B113" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>136455283</v>
       </c>
       <c r="B114" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>136455805</v>
       </c>
       <c r="B115" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>136665864</v>
       </c>
       <c r="B116" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>136665865</v>
       </c>
       <c r="B117" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>136713127</v>
       </c>
       <c r="B118" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136778059</v>
       </c>
       <c r="B119" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136783432</v>
       </c>
       <c r="B120" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136783435</v>
       </c>
       <c r="B121" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136811230</v>
       </c>
       <c r="B122" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136811234</v>
       </c>
       <c r="B123" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136811235</v>
       </c>
       <c r="B124" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136811236</v>
       </c>
       <c r="B125" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136811237</v>
       </c>
       <c r="B126" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136811245</v>
       </c>
       <c r="B127" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136812545</v>
       </c>
       <c r="B128" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>136812546</v>
       </c>
       <c r="B129" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>136812548</v>
       </c>
       <c r="B130" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>136812549</v>
       </c>
       <c r="B131" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>136358182</v>
       </c>
       <c r="B155" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>136359040</v>
       </c>
       <c r="B156" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>136778055</v>
       </c>
       <c r="B157" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>136778061</v>
       </c>
       <c r="B158" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>136778063</v>
       </c>
       <c r="B159" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>136811244</v>
       </c>
       <c r="B160" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>136811246</v>
       </c>
       <c r="B161" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>136811233</v>
       </c>
       <c r="B172" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>136811243</v>
       </c>
       <c r="B173" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>136778052</v>
       </c>
       <c r="B180" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>136778054</v>
       </c>
       <c r="B181" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>136778056</v>
       </c>
       <c r="B182" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>136356211</v>
       </c>
       <c r="B184" t="n">
-        <v>93440</v>
+        <v>93442</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>136357506</v>
       </c>
       <c r="B185" t="n">
-        <v>93440</v>
+        <v>93442</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>136358191</v>
       </c>
       <c r="B186" t="n">
-        <v>93440</v>
+        <v>93442</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>136811231</v>
       </c>
       <c r="B187" t="n">
-        <v>93440</v>
+        <v>93442</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>136723440</v>
       </c>
       <c r="B196" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>136778050</v>
       </c>
       <c r="B197" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>136778051</v>
       </c>
       <c r="B198" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>136358859</v>
       </c>
       <c r="B201" t="n">
-        <v>93395</v>
+        <v>93397</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>136583701</v>
       </c>
       <c r="B202" t="n">
-        <v>93395</v>
+        <v>93397</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>136811247</v>
       </c>
       <c r="B214" t="n">
-        <v>90876</v>
+        <v>90878</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>136783433</v>
       </c>
       <c r="B217" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>136357484</v>
       </c>
       <c r="B236" t="n">
-        <v>106483</v>
+        <v>106489</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>136358853</v>
       </c>
       <c r="B237" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -1733,7 +1733,7 @@
         <v>136722796</v>
       </c>
       <c r="B11" t="n">
-        <v>90846</v>
+        <v>90848</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>136723714</v>
       </c>
       <c r="B12" t="n">
-        <v>90846</v>
+        <v>90848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136778053</v>
       </c>
       <c r="B21" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>136778057</v>
       </c>
       <c r="B22" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136778064</v>
       </c>
       <c r="B23" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136778066</v>
       </c>
       <c r="B24" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136811248</v>
       </c>
       <c r="B25" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>136356702</v>
       </c>
       <c r="B49" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>136356995</v>
       </c>
       <c r="B63" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>136455202</v>
       </c>
       <c r="B64" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136665861</v>
       </c>
       <c r="B65" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>136356269</v>
       </c>
       <c r="B106" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>136356315</v>
       </c>
       <c r="B107" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>136356351</v>
       </c>
       <c r="B108" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>136356430</v>
       </c>
       <c r="B109" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>136357307</v>
       </c>
       <c r="B110" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>136357556</v>
       </c>
       <c r="B111" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>136358081</v>
       </c>
       <c r="B112" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>136455012</v>
       </c>
       <c r="B113" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>136455283</v>
       </c>
       <c r="B114" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>136455805</v>
       </c>
       <c r="B115" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>136665864</v>
       </c>
       <c r="B116" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>136665865</v>
       </c>
       <c r="B117" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>136713127</v>
       </c>
       <c r="B118" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136778059</v>
       </c>
       <c r="B119" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136783432</v>
       </c>
       <c r="B120" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136783435</v>
       </c>
       <c r="B121" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136811230</v>
       </c>
       <c r="B122" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136811234</v>
       </c>
       <c r="B123" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136811235</v>
       </c>
       <c r="B124" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136811236</v>
       </c>
       <c r="B125" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136811237</v>
       </c>
       <c r="B126" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136811245</v>
       </c>
       <c r="B127" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136812545</v>
       </c>
       <c r="B128" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>136812546</v>
       </c>
       <c r="B129" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>136812548</v>
       </c>
       <c r="B130" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>136812549</v>
       </c>
       <c r="B131" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>136358182</v>
       </c>
       <c r="B155" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>136359040</v>
       </c>
       <c r="B156" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>136778055</v>
       </c>
       <c r="B157" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>136778061</v>
       </c>
       <c r="B158" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>136778063</v>
       </c>
       <c r="B159" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>136811244</v>
       </c>
       <c r="B160" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>136811246</v>
       </c>
       <c r="B161" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>136811233</v>
       </c>
       <c r="B172" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>136811243</v>
       </c>
       <c r="B173" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>136778052</v>
       </c>
       <c r="B180" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>136778054</v>
       </c>
       <c r="B181" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>136778056</v>
       </c>
       <c r="B182" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>136356211</v>
       </c>
       <c r="B184" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>136357506</v>
       </c>
       <c r="B185" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>136358191</v>
       </c>
       <c r="B186" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>136811231</v>
       </c>
       <c r="B187" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>136723440</v>
       </c>
       <c r="B196" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>136778050</v>
       </c>
       <c r="B197" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>136778051</v>
       </c>
       <c r="B198" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>136358859</v>
       </c>
       <c r="B201" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>136583701</v>
       </c>
       <c r="B202" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>136811247</v>
       </c>
       <c r="B214" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>136783433</v>
       </c>
       <c r="B217" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>136357484</v>
       </c>
       <c r="B236" t="n">
-        <v>106489</v>
+        <v>106491</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>136358853</v>
       </c>
       <c r="B237" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -1733,7 +1733,7 @@
         <v>136722796</v>
       </c>
       <c r="B11" t="n">
-        <v>90848</v>
+        <v>90849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>136723714</v>
       </c>
       <c r="B12" t="n">
-        <v>90848</v>
+        <v>90849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136778053</v>
       </c>
       <c r="B21" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>136778057</v>
       </c>
       <c r="B22" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136778064</v>
       </c>
       <c r="B23" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136778066</v>
       </c>
       <c r="B24" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136811248</v>
       </c>
       <c r="B25" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>136455202</v>
       </c>
       <c r="B64" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136665861</v>
       </c>
       <c r="B65" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>136455012</v>
       </c>
       <c r="B113" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>136455283</v>
       </c>
       <c r="B114" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>136455805</v>
       </c>
       <c r="B115" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>136665864</v>
       </c>
       <c r="B116" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>136665865</v>
       </c>
       <c r="B117" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>136713127</v>
       </c>
       <c r="B118" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136778059</v>
       </c>
       <c r="B119" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136783432</v>
       </c>
       <c r="B120" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136783435</v>
       </c>
       <c r="B121" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136811230</v>
       </c>
       <c r="B122" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136811234</v>
       </c>
       <c r="B123" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136811235</v>
       </c>
       <c r="B124" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136811236</v>
       </c>
       <c r="B125" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136811237</v>
       </c>
       <c r="B126" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136811245</v>
       </c>
       <c r="B127" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136812545</v>
       </c>
       <c r="B128" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>136812546</v>
       </c>
       <c r="B129" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>136812548</v>
       </c>
       <c r="B130" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>136812549</v>
       </c>
       <c r="B131" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>136778055</v>
       </c>
       <c r="B157" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>136778061</v>
       </c>
       <c r="B158" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>136778063</v>
       </c>
       <c r="B159" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>136811244</v>
       </c>
       <c r="B160" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>136811246</v>
       </c>
       <c r="B161" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>136811233</v>
       </c>
       <c r="B172" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>136811243</v>
       </c>
       <c r="B173" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>136778052</v>
       </c>
       <c r="B180" t="n">
-        <v>90711</v>
+        <v>90712</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>136778054</v>
       </c>
       <c r="B181" t="n">
-        <v>90711</v>
+        <v>90712</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>136778056</v>
       </c>
       <c r="B182" t="n">
-        <v>90711</v>
+        <v>90712</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>136811231</v>
       </c>
       <c r="B187" t="n">
-        <v>93444</v>
+        <v>93445</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>136723440</v>
       </c>
       <c r="B196" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>136778050</v>
       </c>
       <c r="B197" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>136778051</v>
       </c>
       <c r="B198" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>136583701</v>
       </c>
       <c r="B202" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>136811247</v>
       </c>
       <c r="B214" t="n">
-        <v>90880</v>
+        <v>90881</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>136783433</v>
       </c>
       <c r="B217" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -1733,7 +1733,7 @@
         <v>136722796</v>
       </c>
       <c r="B11" t="n">
-        <v>90849</v>
+        <v>90855</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>136723714</v>
       </c>
       <c r="B12" t="n">
-        <v>90849</v>
+        <v>90855</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136778053</v>
       </c>
       <c r="B21" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>136778057</v>
       </c>
       <c r="B22" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136778064</v>
       </c>
       <c r="B23" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136778066</v>
       </c>
       <c r="B24" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136811248</v>
       </c>
       <c r="B25" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>136455202</v>
       </c>
       <c r="B64" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136665861</v>
       </c>
       <c r="B65" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>136455012</v>
       </c>
       <c r="B113" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>136455283</v>
       </c>
       <c r="B114" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>136455805</v>
       </c>
       <c r="B115" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>136665864</v>
       </c>
       <c r="B116" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>136665865</v>
       </c>
       <c r="B117" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>136713127</v>
       </c>
       <c r="B118" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136778059</v>
       </c>
       <c r="B119" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136783432</v>
       </c>
       <c r="B120" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136783435</v>
       </c>
       <c r="B121" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136811230</v>
       </c>
       <c r="B122" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136811234</v>
       </c>
       <c r="B123" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136811235</v>
       </c>
       <c r="B124" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136811236</v>
       </c>
       <c r="B125" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136811237</v>
       </c>
       <c r="B126" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136811245</v>
       </c>
       <c r="B127" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136812545</v>
       </c>
       <c r="B128" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>136812546</v>
       </c>
       <c r="B129" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>136812548</v>
       </c>
       <c r="B130" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>136812549</v>
       </c>
       <c r="B131" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>136778055</v>
       </c>
       <c r="B157" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>136778061</v>
       </c>
       <c r="B158" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>136778063</v>
       </c>
       <c r="B159" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>136811244</v>
       </c>
       <c r="B160" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>136811246</v>
       </c>
       <c r="B161" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>136811233</v>
       </c>
       <c r="B172" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>136811243</v>
       </c>
       <c r="B173" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>136778052</v>
       </c>
       <c r="B180" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>136778054</v>
       </c>
       <c r="B181" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>136778056</v>
       </c>
       <c r="B182" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>136811231</v>
       </c>
       <c r="B187" t="n">
-        <v>93445</v>
+        <v>93451</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>136723440</v>
       </c>
       <c r="B196" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>136778050</v>
       </c>
       <c r="B197" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>136778051</v>
       </c>
       <c r="B198" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>136583701</v>
       </c>
       <c r="B202" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>136811247</v>
       </c>
       <c r="B214" t="n">
-        <v>90881</v>
+        <v>90887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -1733,7 +1733,7 @@
         <v>136722796</v>
       </c>
       <c r="B11" t="n">
-        <v>90855</v>
+        <v>90859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>136723714</v>
       </c>
       <c r="B12" t="n">
-        <v>90855</v>
+        <v>90859</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136778053</v>
       </c>
       <c r="B21" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>136778057</v>
       </c>
       <c r="B22" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136778064</v>
       </c>
       <c r="B23" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136778066</v>
       </c>
       <c r="B24" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136811248</v>
       </c>
       <c r="B25" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136665861</v>
       </c>
       <c r="B65" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>136665864</v>
       </c>
       <c r="B116" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>136665865</v>
       </c>
       <c r="B117" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>136713127</v>
       </c>
       <c r="B118" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136778059</v>
       </c>
       <c r="B119" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136783432</v>
       </c>
       <c r="B120" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136783435</v>
       </c>
       <c r="B121" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136811230</v>
       </c>
       <c r="B122" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136811234</v>
       </c>
       <c r="B123" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136811235</v>
       </c>
       <c r="B124" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136811236</v>
       </c>
       <c r="B125" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136811237</v>
       </c>
       <c r="B126" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136811245</v>
       </c>
       <c r="B127" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136812545</v>
       </c>
       <c r="B128" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>136812546</v>
       </c>
       <c r="B129" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>136812548</v>
       </c>
       <c r="B130" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>136812549</v>
       </c>
       <c r="B131" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>136778055</v>
       </c>
       <c r="B157" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>136778061</v>
       </c>
       <c r="B158" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>136778063</v>
       </c>
       <c r="B159" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>136811244</v>
       </c>
       <c r="B160" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>136811246</v>
       </c>
       <c r="B161" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>136811233</v>
       </c>
       <c r="B172" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>136811243</v>
       </c>
       <c r="B173" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>136778052</v>
       </c>
       <c r="B180" t="n">
-        <v>90718</v>
+        <v>90722</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>136778054</v>
       </c>
       <c r="B181" t="n">
-        <v>90718</v>
+        <v>90722</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>136778056</v>
       </c>
       <c r="B182" t="n">
-        <v>90718</v>
+        <v>90722</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>136811231</v>
       </c>
       <c r="B187" t="n">
-        <v>93451</v>
+        <v>93455</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>136723440</v>
       </c>
       <c r="B196" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>136778050</v>
       </c>
       <c r="B197" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>136778051</v>
       </c>
       <c r="B198" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>136583701</v>
       </c>
       <c r="B202" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>136811247</v>
       </c>
       <c r="B214" t="n">
-        <v>90887</v>
+        <v>90891</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>136783433</v>
       </c>
       <c r="B217" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -13817,7 +13817,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson, Magdalena Nilsson, Patrik Eriksson, Gunnar Janson</t>
+          <t>Alva Danielsson, Gunnar Janson, Patrik Eriksson, Magdalena Nilsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson, Magdalena Nilsson, Patrik Eriksson, Gunnar Janson</t>
+          <t>Alva Danielsson, Gunnar Janson, Patrik Eriksson, Magdalena Nilsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -24445,7 +24445,7 @@
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson, Magdalena Nilsson, Patrik Eriksson, Gunnar Janson</t>
+          <t>Alva Danielsson, Gunnar Janson, Patrik Eriksson, Magdalena Nilsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -13817,7 +13817,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Gunnar Janson, Patrik Eriksson, Magdalena Nilsson, Felix Gustafsson</t>
+          <t>Alva Danielsson, Felix Gustafsson, Magdalena Nilsson, Patrik Eriksson, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Gunnar Janson, Patrik Eriksson, Magdalena Nilsson, Felix Gustafsson</t>
+          <t>Alva Danielsson, Felix Gustafsson, Magdalena Nilsson, Patrik Eriksson, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -24445,7 +24445,7 @@
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Gunnar Janson, Patrik Eriksson, Magdalena Nilsson, Felix Gustafsson</t>
+          <t>Alva Danielsson, Felix Gustafsson, Magdalena Nilsson, Patrik Eriksson, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -1733,7 +1733,7 @@
         <v>136722796</v>
       </c>
       <c r="B11" t="n">
-        <v>90859</v>
+        <v>90861</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>136723714</v>
       </c>
       <c r="B12" t="n">
-        <v>90859</v>
+        <v>90861</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136778053</v>
       </c>
       <c r="B21" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>136778057</v>
       </c>
       <c r="B22" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136778064</v>
       </c>
       <c r="B23" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136778066</v>
       </c>
       <c r="B24" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136811248</v>
       </c>
       <c r="B25" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136665861</v>
       </c>
       <c r="B65" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>136665864</v>
       </c>
       <c r="B116" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>136665865</v>
       </c>
       <c r="B117" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>136713127</v>
       </c>
       <c r="B118" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136778059</v>
       </c>
       <c r="B119" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136783432</v>
       </c>
       <c r="B120" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136783435</v>
       </c>
       <c r="B121" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136811230</v>
       </c>
       <c r="B122" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136811234</v>
       </c>
       <c r="B123" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136811235</v>
       </c>
       <c r="B124" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136811236</v>
       </c>
       <c r="B125" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136811237</v>
       </c>
       <c r="B126" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136811245</v>
       </c>
       <c r="B127" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136812545</v>
       </c>
       <c r="B128" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>136812546</v>
       </c>
       <c r="B129" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>136812548</v>
       </c>
       <c r="B130" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>136812549</v>
       </c>
       <c r="B131" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>136778055</v>
       </c>
       <c r="B157" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>136778061</v>
       </c>
       <c r="B158" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>136778063</v>
       </c>
       <c r="B159" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>136811244</v>
       </c>
       <c r="B160" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>136811246</v>
       </c>
       <c r="B161" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>136811233</v>
       </c>
       <c r="B172" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>136811243</v>
       </c>
       <c r="B173" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>136778052</v>
       </c>
       <c r="B180" t="n">
-        <v>90722</v>
+        <v>90724</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>136778054</v>
       </c>
       <c r="B181" t="n">
-        <v>90722</v>
+        <v>90724</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>136778056</v>
       </c>
       <c r="B182" t="n">
-        <v>90722</v>
+        <v>90724</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>136811231</v>
       </c>
       <c r="B187" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>136723440</v>
       </c>
       <c r="B196" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>136778050</v>
       </c>
       <c r="B197" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>136778051</v>
       </c>
       <c r="B198" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>136583701</v>
       </c>
       <c r="B202" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>136811247</v>
       </c>
       <c r="B214" t="n">
-        <v>90891</v>
+        <v>90893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>136783433</v>
       </c>
       <c r="B217" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -1733,7 +1733,7 @@
         <v>136722796</v>
       </c>
       <c r="B11" t="n">
-        <v>90861</v>
+        <v>90874</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>136723714</v>
       </c>
       <c r="B12" t="n">
-        <v>90861</v>
+        <v>90874</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136778053</v>
       </c>
       <c r="B21" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>136778057</v>
       </c>
       <c r="B22" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136778064</v>
       </c>
       <c r="B23" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136778066</v>
       </c>
       <c r="B24" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136811248</v>
       </c>
       <c r="B25" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136665861</v>
       </c>
       <c r="B65" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>136665864</v>
       </c>
       <c r="B116" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>136665865</v>
       </c>
       <c r="B117" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>136713127</v>
       </c>
       <c r="B118" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136778059</v>
       </c>
       <c r="B119" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136783432</v>
       </c>
       <c r="B120" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136783435</v>
       </c>
       <c r="B121" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136811230</v>
       </c>
       <c r="B122" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136811234</v>
       </c>
       <c r="B123" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136811235</v>
       </c>
       <c r="B124" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136811236</v>
       </c>
       <c r="B125" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136811237</v>
       </c>
       <c r="B126" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136811245</v>
       </c>
       <c r="B127" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136812545</v>
       </c>
       <c r="B128" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>136812546</v>
       </c>
       <c r="B129" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>136812548</v>
       </c>
       <c r="B130" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>136812549</v>
       </c>
       <c r="B131" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>136778055</v>
       </c>
       <c r="B157" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>136778061</v>
       </c>
       <c r="B158" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>136778063</v>
       </c>
       <c r="B159" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>136811244</v>
       </c>
       <c r="B160" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>136811246</v>
       </c>
       <c r="B161" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>136811233</v>
       </c>
       <c r="B172" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>136811243</v>
       </c>
       <c r="B173" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>136778052</v>
       </c>
       <c r="B180" t="n">
-        <v>90724</v>
+        <v>90737</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>136778054</v>
       </c>
       <c r="B181" t="n">
-        <v>90724</v>
+        <v>90737</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>136778056</v>
       </c>
       <c r="B182" t="n">
-        <v>90724</v>
+        <v>90737</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>136811231</v>
       </c>
       <c r="B187" t="n">
-        <v>93457</v>
+        <v>93470</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>136723440</v>
       </c>
       <c r="B196" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>136778050</v>
       </c>
       <c r="B197" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>136778051</v>
       </c>
       <c r="B198" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>136583701</v>
       </c>
       <c r="B202" t="n">
-        <v>93412</v>
+        <v>93425</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>136811247</v>
       </c>
       <c r="B214" t="n">
-        <v>90893</v>
+        <v>90906</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>136783433</v>
       </c>
       <c r="B217" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -1733,7 +1733,7 @@
         <v>136722796</v>
       </c>
       <c r="B11" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>136723714</v>
       </c>
       <c r="B12" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136778053</v>
       </c>
       <c r="B21" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>136778057</v>
       </c>
       <c r="B22" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136778064</v>
       </c>
       <c r="B23" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136778066</v>
       </c>
       <c r="B24" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136811248</v>
       </c>
       <c r="B25" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136665861</v>
       </c>
       <c r="B65" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>136665864</v>
       </c>
       <c r="B116" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>136665865</v>
       </c>
       <c r="B117" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>136713127</v>
       </c>
       <c r="B118" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136778059</v>
       </c>
       <c r="B119" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136783432</v>
       </c>
       <c r="B120" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136783435</v>
       </c>
       <c r="B121" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136811230</v>
       </c>
       <c r="B122" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136811234</v>
       </c>
       <c r="B123" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136811235</v>
       </c>
       <c r="B124" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136811236</v>
       </c>
       <c r="B125" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136811237</v>
       </c>
       <c r="B126" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136811245</v>
       </c>
       <c r="B127" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136812545</v>
       </c>
       <c r="B128" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>136812546</v>
       </c>
       <c r="B129" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>136812548</v>
       </c>
       <c r="B130" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>136812549</v>
       </c>
       <c r="B131" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>136778055</v>
       </c>
       <c r="B157" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>136778061</v>
       </c>
       <c r="B158" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>136778063</v>
       </c>
       <c r="B159" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>136811244</v>
       </c>
       <c r="B160" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>136811246</v>
       </c>
       <c r="B161" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>136811233</v>
       </c>
       <c r="B172" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>136811243</v>
       </c>
       <c r="B173" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>136778052</v>
       </c>
       <c r="B180" t="n">
-        <v>90737</v>
+        <v>90739</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>136778054</v>
       </c>
       <c r="B181" t="n">
-        <v>90737</v>
+        <v>90739</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>136778056</v>
       </c>
       <c r="B182" t="n">
-        <v>90737</v>
+        <v>90739</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>136811231</v>
       </c>
       <c r="B187" t="n">
-        <v>93470</v>
+        <v>93471</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>136723440</v>
       </c>
       <c r="B196" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>136778050</v>
       </c>
       <c r="B197" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>136778051</v>
       </c>
       <c r="B198" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>136811247</v>
       </c>
       <c r="B214" t="n">
-        <v>90906</v>
+        <v>90908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>136783433</v>
       </c>
       <c r="B217" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -1733,7 +1733,7 @@
         <v>136722796</v>
       </c>
       <c r="B11" t="n">
-        <v>90876</v>
+        <v>90879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>136723714</v>
       </c>
       <c r="B12" t="n">
-        <v>90876</v>
+        <v>90879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136778053</v>
       </c>
       <c r="B21" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>136778057</v>
       </c>
       <c r="B22" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136778064</v>
       </c>
       <c r="B23" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136778066</v>
       </c>
       <c r="B24" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136811248</v>
       </c>
       <c r="B25" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>136665861</v>
       </c>
       <c r="B65" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>136665864</v>
       </c>
       <c r="B116" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>136665865</v>
       </c>
       <c r="B117" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>136713127</v>
       </c>
       <c r="B118" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136778059</v>
       </c>
       <c r="B119" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136783432</v>
       </c>
       <c r="B120" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136783435</v>
       </c>
       <c r="B121" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136811230</v>
       </c>
       <c r="B122" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136811234</v>
       </c>
       <c r="B123" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136811235</v>
       </c>
       <c r="B124" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136811236</v>
       </c>
       <c r="B125" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136811237</v>
       </c>
       <c r="B126" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136811245</v>
       </c>
       <c r="B127" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136812545</v>
       </c>
       <c r="B128" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>136812546</v>
       </c>
       <c r="B129" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>136812548</v>
       </c>
       <c r="B130" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>136812549</v>
       </c>
       <c r="B131" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>136778055</v>
       </c>
       <c r="B157" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>136778061</v>
       </c>
       <c r="B158" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>136778063</v>
       </c>
       <c r="B159" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>136811244</v>
       </c>
       <c r="B160" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>136811246</v>
       </c>
       <c r="B161" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>136811233</v>
       </c>
       <c r="B172" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>136811243</v>
       </c>
       <c r="B173" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>136778052</v>
       </c>
       <c r="B180" t="n">
-        <v>90739</v>
+        <v>90742</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>136778054</v>
       </c>
       <c r="B181" t="n">
-        <v>90739</v>
+        <v>90742</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>136778056</v>
       </c>
       <c r="B182" t="n">
-        <v>90739</v>
+        <v>90742</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>136811231</v>
       </c>
       <c r="B187" t="n">
-        <v>93471</v>
+        <v>93474</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>136723440</v>
       </c>
       <c r="B196" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>136778050</v>
       </c>
       <c r="B197" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>136778051</v>
       </c>
       <c r="B198" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>136811247</v>
       </c>
       <c r="B214" t="n">
-        <v>90908</v>
+        <v>90911</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -1733,7 +1733,7 @@
         <v>136722796</v>
       </c>
       <c r="B11" t="n">
-        <v>90879</v>
+        <v>90889</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>136723714</v>
       </c>
       <c r="B12" t="n">
-        <v>90879</v>
+        <v>90889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136778053</v>
       </c>
       <c r="B21" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>136778057</v>
       </c>
       <c r="B22" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136778064</v>
       </c>
       <c r="B23" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136778066</v>
       </c>
       <c r="B24" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136811248</v>
       </c>
       <c r="B25" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>136713127</v>
       </c>
       <c r="B118" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136778059</v>
       </c>
       <c r="B119" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136783432</v>
       </c>
       <c r="B120" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136783435</v>
       </c>
       <c r="B121" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136811230</v>
       </c>
       <c r="B122" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136811234</v>
       </c>
       <c r="B123" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136811235</v>
       </c>
       <c r="B124" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136811236</v>
       </c>
       <c r="B125" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136811237</v>
       </c>
       <c r="B126" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136811245</v>
       </c>
       <c r="B127" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136812545</v>
       </c>
       <c r="B128" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>136812546</v>
       </c>
       <c r="B129" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>136812548</v>
       </c>
       <c r="B130" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>136812549</v>
       </c>
       <c r="B131" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>136778055</v>
       </c>
       <c r="B157" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>136778061</v>
       </c>
       <c r="B158" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>136778063</v>
       </c>
       <c r="B159" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>136811244</v>
       </c>
       <c r="B160" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>136811246</v>
       </c>
       <c r="B161" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>136811233</v>
       </c>
       <c r="B172" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>136811243</v>
       </c>
       <c r="B173" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>136778052</v>
       </c>
       <c r="B180" t="n">
-        <v>90742</v>
+        <v>90752</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>136778054</v>
       </c>
       <c r="B181" t="n">
-        <v>90742</v>
+        <v>90752</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>136778056</v>
       </c>
       <c r="B182" t="n">
-        <v>90742</v>
+        <v>90752</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>136811231</v>
       </c>
       <c r="B187" t="n">
-        <v>93474</v>
+        <v>93484</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>136723440</v>
       </c>
       <c r="B196" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>136778050</v>
       </c>
       <c r="B197" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>136778051</v>
       </c>
       <c r="B198" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>136811247</v>
       </c>
       <c r="B214" t="n">
-        <v>90911</v>
+        <v>90921</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>136783433</v>
       </c>
       <c r="B217" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -1733,7 +1733,7 @@
         <v>136722796</v>
       </c>
       <c r="B11" t="n">
-        <v>90889</v>
+        <v>90890</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>136723714</v>
       </c>
       <c r="B12" t="n">
-        <v>90889</v>
+        <v>90890</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136778053</v>
       </c>
       <c r="B21" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>136778057</v>
       </c>
       <c r="B22" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136778064</v>
       </c>
       <c r="B23" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136778066</v>
       </c>
       <c r="B24" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136811248</v>
       </c>
       <c r="B25" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136778059</v>
       </c>
       <c r="B119" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136783432</v>
       </c>
       <c r="B120" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136783435</v>
       </c>
       <c r="B121" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136811230</v>
       </c>
       <c r="B122" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136811234</v>
       </c>
       <c r="B123" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136811235</v>
       </c>
       <c r="B124" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136811236</v>
       </c>
       <c r="B125" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136811237</v>
       </c>
       <c r="B126" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136811245</v>
       </c>
       <c r="B127" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136812545</v>
       </c>
       <c r="B128" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>136812546</v>
       </c>
       <c r="B129" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>136812548</v>
       </c>
       <c r="B130" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>136812549</v>
       </c>
       <c r="B131" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>136778055</v>
       </c>
       <c r="B157" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>136778061</v>
       </c>
       <c r="B158" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>136778063</v>
       </c>
       <c r="B159" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>136811244</v>
       </c>
       <c r="B160" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>136811246</v>
       </c>
       <c r="B161" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>136811233</v>
       </c>
       <c r="B172" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>136811243</v>
       </c>
       <c r="B173" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>136778052</v>
       </c>
       <c r="B180" t="n">
-        <v>90752</v>
+        <v>90753</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>136778054</v>
       </c>
       <c r="B181" t="n">
-        <v>90752</v>
+        <v>90753</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>136778056</v>
       </c>
       <c r="B182" t="n">
-        <v>90752</v>
+        <v>90753</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>136811231</v>
       </c>
       <c r="B187" t="n">
-        <v>93484</v>
+        <v>93485</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>136723440</v>
       </c>
       <c r="B196" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>136778050</v>
       </c>
       <c r="B197" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>136778051</v>
       </c>
       <c r="B198" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>136811247</v>
       </c>
       <c r="B214" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -2900,7 +2900,7 @@
         <v>136778053</v>
       </c>
       <c r="B21" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>136778057</v>
       </c>
       <c r="B22" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136778064</v>
       </c>
       <c r="B23" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136778066</v>
       </c>
       <c r="B24" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136811248</v>
       </c>
       <c r="B25" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136778059</v>
       </c>
       <c r="B119" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136783432</v>
       </c>
       <c r="B120" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136783435</v>
       </c>
       <c r="B121" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136811230</v>
       </c>
       <c r="B122" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136811234</v>
       </c>
       <c r="B123" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136811235</v>
       </c>
       <c r="B124" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136811236</v>
       </c>
       <c r="B125" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136811237</v>
       </c>
       <c r="B126" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136811245</v>
       </c>
       <c r="B127" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136812545</v>
       </c>
       <c r="B128" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>136812546</v>
       </c>
       <c r="B129" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>136812548</v>
       </c>
       <c r="B130" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>136812549</v>
       </c>
       <c r="B131" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>136778055</v>
       </c>
       <c r="B157" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>136778061</v>
       </c>
       <c r="B158" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>136778063</v>
       </c>
       <c r="B159" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>136811244</v>
       </c>
       <c r="B160" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>136811246</v>
       </c>
       <c r="B161" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>136811233</v>
       </c>
       <c r="B172" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>136811243</v>
       </c>
       <c r="B173" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>136778052</v>
       </c>
       <c r="B180" t="n">
-        <v>90753</v>
+        <v>90756</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>136778054</v>
       </c>
       <c r="B181" t="n">
-        <v>90753</v>
+        <v>90756</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>136778056</v>
       </c>
       <c r="B182" t="n">
-        <v>90753</v>
+        <v>90756</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>136811231</v>
       </c>
       <c r="B187" t="n">
-        <v>93485</v>
+        <v>93490</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>136778050</v>
       </c>
       <c r="B197" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>136778051</v>
       </c>
       <c r="B198" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>136811247</v>
       </c>
       <c r="B214" t="n">
-        <v>90922</v>
+        <v>90925</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>136783433</v>
       </c>
       <c r="B217" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -2900,7 +2900,7 @@
         <v>136778053</v>
       </c>
       <c r="B21" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>136778057</v>
       </c>
       <c r="B22" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>136778064</v>
       </c>
       <c r="B23" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>136778066</v>
       </c>
       <c r="B24" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>136811248</v>
       </c>
       <c r="B25" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136778059</v>
       </c>
       <c r="B119" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136783432</v>
       </c>
       <c r="B120" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136783435</v>
       </c>
       <c r="B121" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136811230</v>
       </c>
       <c r="B122" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136811234</v>
       </c>
       <c r="B123" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136811235</v>
       </c>
       <c r="B124" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136811236</v>
       </c>
       <c r="B125" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136811237</v>
       </c>
       <c r="B126" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136811245</v>
       </c>
       <c r="B127" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136812545</v>
       </c>
       <c r="B128" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>136812546</v>
       </c>
       <c r="B129" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>136812548</v>
       </c>
       <c r="B130" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>136812549</v>
       </c>
       <c r="B131" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>136778055</v>
       </c>
       <c r="B157" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>136778061</v>
       </c>
       <c r="B158" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>136778063</v>
       </c>
       <c r="B159" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>136811244</v>
       </c>
       <c r="B160" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>136811246</v>
       </c>
       <c r="B161" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>136811233</v>
       </c>
       <c r="B172" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>136811243</v>
       </c>
       <c r="B173" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>136811231</v>
       </c>
       <c r="B187" t="n">
-        <v>93490</v>
+        <v>93492</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>136778050</v>
       </c>
       <c r="B197" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>136778051</v>
       </c>
       <c r="B198" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -3348,7 +3348,7 @@
         <v>136811248</v>
       </c>
       <c r="B25" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136783432</v>
       </c>
       <c r="B120" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136783435</v>
       </c>
       <c r="B121" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136811230</v>
       </c>
       <c r="B122" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136811234</v>
       </c>
       <c r="B123" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136811235</v>
       </c>
       <c r="B124" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136811236</v>
       </c>
       <c r="B125" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136811237</v>
       </c>
       <c r="B126" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136811245</v>
       </c>
       <c r="B127" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>136812545</v>
       </c>
       <c r="B128" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>136812546</v>
       </c>
       <c r="B129" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>136812548</v>
       </c>
       <c r="B130" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>136812549</v>
       </c>
       <c r="B131" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>136811244</v>
       </c>
       <c r="B160" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>136811246</v>
       </c>
       <c r="B161" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>136811233</v>
       </c>
       <c r="B172" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>136811243</v>
       </c>
       <c r="B173" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>136811231</v>
       </c>
       <c r="B187" t="n">
-        <v>93492</v>
+        <v>93498</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>136811247</v>
       </c>
       <c r="B214" t="n">
-        <v>90925</v>
+        <v>90930</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>136783433</v>
       </c>
       <c r="B217" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>

--- a/artfynd/A 45663-2024 artfynd.xlsx
+++ b/artfynd/A 45663-2024 artfynd.xlsx
@@ -7902,7 +7902,7 @@
         <v>136829229</v>
       </c>
       <c r="B66" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>136829225</v>
       </c>
       <c r="B132" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>136829227</v>
       </c>
       <c r="B133" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>136829230</v>
       </c>
       <c r="B134" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>136829232</v>
       </c>
       <c r="B135" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
